--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-9810.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-9810.xlsx
@@ -731,9 +731,7 @@
       <c r="C67">
         <v>4</v>
       </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
+      <c r="D67"/>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
@@ -789,9 +787,7 @@
       <c r="C79">
         <v>5</v>
       </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
+      <c r="D79"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
